--- a/data/sxbet/ligas/First League/trades.xlsx
+++ b/data/sxbet/ligas/First League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,110 +531,214 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>0x4449ee9e19610ed1a6459a4ec622295d3b7f27785ad56fb418383aa2562ee601</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.5987</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>FK Pardubice vs FK Jablonec</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>FK Pardubice</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>FK Jablonec</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0x6f33961a8aeffc315ff5d4a74c7a39f6142a8a7935508f048474d0ff32992a6d</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>L19527406</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1785415503</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1785693600</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>58.455115</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>0x19f2092f5b69321f498e3935667243b7f359a9876c356076e23b9a65276c6308</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>0.99998</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>1.8363</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>AC Sparta Praha</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>First League</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>AC Sparta Praha vs FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>AC Sparta Praha</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>0x030b420c1d99e5824e84934cc2cf515e30fa8607adbe9c86574bc07d04d89b58</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>L19527404</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>1785344291</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>1785517200</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>1.195791</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/First League/trades.xlsx
+++ b/data/sxbet/ligas/First League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x4449ee9e19610ed1a6459a4ec622295d3b7f27785ad56fb418383aa2562ee601</t>
+          <t>0x5743b3baab7d0b4196ffe72f2ea5f72938b9bc8bd6e7156319c249a8e1d4977e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.0625</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,7 +559,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>First League</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FK Pardubice vs FK Jablonec</t>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>FK Pardubice</t>
+          <t>AC Sparta Praha</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>FK Jablonec</t>
+          <t>FC Fastav Zlín</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x6f33961a8aeffc315ff5d4a74c7a39f6142a8a7935508f048474d0ff32992a6d</t>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19527406</t>
+          <t>L19527404</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785415503</t>
+          <t>1785467456</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785693600</t>
+          <t>1785517200</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>58.455115</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,110 +643,774 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>0xdd3c48b46e7e419535742c6600d8d5c0bfbf337cf9d7384d0931d8644057b38b</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.0625</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1785467455</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0x1c93771d6891dfab8458278bde673acf937ec233145cec08e5cbbf6abad22ca4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.0625</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1785467402</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0x94f51445b33e0f282b7b2e2a657f02ae3b738ee45fa16dda9267fc320dd63f2e</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.0625</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1785467401</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0x7a2d2b6948d276131073d7eb95625bb09fee93e0072e6618ec7171f59bef3d9a</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.0625</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1785467400</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0xb45d6395ce739a0bf97a9c585d0c3aa5d6e2da00ec07295407594c566a55e0a5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.0625</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1785467398</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0x4449ee9e19610ed1a6459a4ec622295d3b7f27785ad56fb418383aa2562ee601</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.5987</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>FK Pardubice vs FK Jablonec</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>FK Pardubice</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>FK Jablonec</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0x6f33961a8aeffc315ff5d4a74c7a39f6142a8a7935508f048474d0ff32992a6d</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>L19527406</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1785415503</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1785693600</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>58.455115</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>0x19f2092f5b69321f498e3935667243b7f359a9876c356076e23b9a65276c6308</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>0.99998</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>1.8363</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>AC Sparta Praha</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>First League</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>AC Sparta Praha vs FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>AC Sparta Praha</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>0x030b420c1d99e5824e84934cc2cf515e30fa8607adbe9c86574bc07d04d89b58</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>L19527404</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>1785344291</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>1785517200</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>1.195791</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/First League/trades.xlsx
+++ b/data/sxbet/ligas/First League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x5743b3baab7d0b4196ffe72f2ea5f72938b9bc8bd6e7156319c249a8e1d4977e</t>
+          <t>0x5826b25b9a78e0be2b5364f99906ff8cc4bf845a562a5ea97f684cd2f19405ae</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13.2855</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FC Fastav Zlín</t>
+          <t>1.FC Slovacko</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+          <t>1.FC Slovacko vs Sk Artis Brno</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>AC Sparta Praha</t>
+          <t>1.FC Slovacko</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>FC Fastav Zlín</t>
+          <t>Sk Artis Brno</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0x10b10a8752de2c6583c0e8fbd3093ad3016bc296293b0a09ba25166e401e636f</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19527404</t>
+          <t>L19527405</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785467456</t>
+          <t>1785483401</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785517200</t>
+          <t>1785596400</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>22.1425</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,62 +643,54 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xdd3c48b46e7e419535742c6600d8d5c0bfbf337cf9d7384d0931d8644057b38b</t>
+          <t>0xe630cfdee3f17d67e170b23665fcaae89fd50d2dc2f339c76f4a1abe7a079fc6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14.025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.425</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>First League</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>FC Fastav Zlín</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0xaeedc6f6ec1744a71bd9be08dbc5f609f00c2c03449f55bd855097430952e5b5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785467455</t>
+          <t>1785476192</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x1c93771d6891dfab8458278bde673acf937ec233145cec08e5cbbf6abad22ca4</t>
+          <t>0x5743b3baab7d0b4196ffe72f2ea5f72938b9bc8bd6e7156319c249a8e1d4977e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -770,7 +762,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -840,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785467402</t>
+          <t>1785467456</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,7 +859,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x94f51445b33e0f282b7b2e2a657f02ae3b738ee45fa16dda9267fc320dd63f2e</t>
+          <t>0xdd3c48b46e7e419535742c6600d8d5c0bfbf337cf9d7384d0931d8644057b38b</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -882,7 +874,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -952,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785467401</t>
+          <t>1785467455</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -962,7 +954,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,7 +971,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x7a2d2b6948d276131073d7eb95625bb09fee93e0072e6618ec7171f59bef3d9a</t>
+          <t>0x1c93771d6891dfab8458278bde673acf937ec233145cec08e5cbbf6abad22ca4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1064,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785467400</t>
+          <t>1785467402</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1091,7 +1083,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xb45d6395ce739a0bf97a9c585d0c3aa5d6e2da00ec07295407594c566a55e0a5</t>
+          <t>0x94f51445b33e0f282b7b2e2a657f02ae3b738ee45fa16dda9267fc320dd63f2e</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1106,7 +1098,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1176,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785467398</t>
+          <t>1785467401</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1186,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1203,23 +1195,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x4449ee9e19610ed1a6459a4ec622295d3b7f27785ad56fb418383aa2562ee601</t>
+          <t>0x7a2d2b6948d276131073d7eb95625bb09fee93e0072e6618ec7171f59bef3d9a</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.0625</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1227,7 +1223,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>First League</t>
@@ -1235,27 +1235,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FK Pardubice vs FK Jablonec</t>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>FK Pardubice</t>
+          <t>AC Sparta Praha</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>FK Jablonec</t>
+          <t>FC Fastav Zlín</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x6f33961a8aeffc315ff5d4a74c7a39f6142a8a7935508f048474d0ff32992a6d</t>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19527406</t>
+          <t>L19527404</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785415503</t>
+          <t>1785467400</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785693600</t>
+          <t>1785517200</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>58.455115</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,110 +1307,326 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>0xb45d6395ce739a0bf97a9c585d0c3aa5d6e2da00ec07295407594c566a55e0a5</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.0625</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1785467398</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0x4449ee9e19610ed1a6459a4ec622295d3b7f27785ad56fb418383aa2562ee601</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.5987</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>FK Pardubice vs FK Jablonec</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>FK Pardubice</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>FK Jablonec</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0x6f33961a8aeffc315ff5d4a74c7a39f6142a8a7935508f048474d0ff32992a6d</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>L19527406</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1785415503</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1785693600</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>58.455115</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>0x19f2092f5b69321f498e3935667243b7f359a9876c356076e23b9a65276c6308</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>0.99998</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>1.8363</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>AC Sparta Praha</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>First League</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>AC Sparta Praha vs FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>AC Sparta Praha</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>0x030b420c1d99e5824e84934cc2cf515e30fa8607adbe9c86574bc07d04d89b58</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>L19527404</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t>1785344291</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>1785517200</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>1.195791</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/First League/trades.xlsx
+++ b/data/sxbet/ligas/First League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x5826b25b9a78e0be2b5364f99906ff8cc4bf845a562a5ea97f684cd2f19405ae</t>
+          <t>0x750959461898d7985dfb52df9d12bdc41ab62fe003f6662c5f2c1f5e6883c3b3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13.2855</t>
+          <t>15.12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.FC Slovacko</t>
+          <t>FC Fastav Zlín</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.FC Slovacko vs Sk Artis Brno</t>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.FC Slovacko</t>
+          <t>AC Sparta Praha</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Sk Artis Brno</t>
+          <t>FC Fastav Zlín</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x10b10a8752de2c6583c0e8fbd3093ad3016bc296293b0a09ba25166e401e636f</t>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19527405</t>
+          <t>L19527404</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785483401</t>
+          <t>1785502250</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785596400</t>
+          <t>1785517200</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>22.1425</t>
+          <t>216.0</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,31 +643,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xe630cfdee3f17d67e170b23665fcaae89fd50d2dc2f339c76f4a1abe7a079fc6</t>
+          <t>0x8f3fc6c2b9b98811247c39740afa1dcc5d19110f7099bc28c5d7d72ac810cac5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>14.025</t>
+          <t>11.61173</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.425</t>
+          <t>1.0713</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>First League</t>
@@ -690,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xaeedc6f6ec1744a71bd9be08dbc5f609f00c2c03449f55bd855097430952e5b5</t>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785476192</t>
+          <t>1785499628</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>162.971649</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,12 +755,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x5743b3baab7d0b4196ffe72f2ea5f72938b9bc8bd6e7156319c249a8e1d4977e</t>
+          <t>0x5826b25b9a78e0be2b5364f99906ff8cc4bf845a562a5ea97f684cd2f19405ae</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -762,12 +770,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13.2855</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -777,7 +785,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FC Fastav Zlín</t>
+          <t>1.FC Slovacko</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -787,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+          <t>1.FC Slovacko vs Sk Artis Brno</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AC Sparta Praha</t>
+          <t>1.FC Slovacko</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>FC Fastav Zlín</t>
+          <t>Sk Artis Brno</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0x10b10a8752de2c6583c0e8fbd3093ad3016bc296293b0a09ba25166e401e636f</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19527404</t>
+          <t>L19527405</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785467456</t>
+          <t>1785483401</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785517200</t>
+          <t>1785596400</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>22.1425</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,62 +867,54 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xdd3c48b46e7e419535742c6600d8d5c0bfbf337cf9d7384d0931d8644057b38b</t>
+          <t>0xe630cfdee3f17d67e170b23665fcaae89fd50d2dc2f339c76f4a1abe7a079fc6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14.025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.425</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>First League</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>FC Fastav Zlín</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0xaeedc6f6ec1744a71bd9be08dbc5f609f00c2c03449f55bd855097430952e5b5</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785467455</t>
+          <t>1785476192</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x1c93771d6891dfab8458278bde673acf937ec233145cec08e5cbbf6abad22ca4</t>
+          <t>0x5743b3baab7d0b4196ffe72f2ea5f72938b9bc8bd6e7156319c249a8e1d4977e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785467402</t>
+          <t>1785467456</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,7 +1083,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x94f51445b33e0f282b7b2e2a657f02ae3b738ee45fa16dda9267fc320dd63f2e</t>
+          <t>0xdd3c48b46e7e419535742c6600d8d5c0bfbf337cf9d7384d0931d8644057b38b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785467401</t>
+          <t>1785467455</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,7 +1195,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x7a2d2b6948d276131073d7eb95625bb09fee93e0072e6618ec7171f59bef3d9a</t>
+          <t>0x1c93771d6891dfab8458278bde673acf937ec233145cec08e5cbbf6abad22ca4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785467400</t>
+          <t>1785467402</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xb45d6395ce739a0bf97a9c585d0c3aa5d6e2da00ec07295407594c566a55e0a5</t>
+          <t>0x94f51445b33e0f282b7b2e2a657f02ae3b738ee45fa16dda9267fc320dd63f2e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785467398</t>
+          <t>1785467401</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,23 +1419,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x4449ee9e19610ed1a6459a4ec622295d3b7f27785ad56fb418383aa2562ee601</t>
+          <t>0x7a2d2b6948d276131073d7eb95625bb09fee93e0072e6618ec7171f59bef3d9a</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.0625</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1443,7 +1447,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>First League</t>
@@ -1451,27 +1459,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FK Pardubice vs FK Jablonec</t>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>FK Pardubice</t>
+          <t>AC Sparta Praha</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>FK Jablonec</t>
+          <t>FC Fastav Zlín</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x6f33961a8aeffc315ff5d4a74c7a39f6142a8a7935508f048474d0ff32992a6d</t>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19527406</t>
+          <t>L19527404</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1496,17 +1504,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785415503</t>
+          <t>1785467400</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785693600</t>
+          <t>1785517200</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>58.455115</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,110 +1531,326 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>0xb45d6395ce739a0bf97a9c585d0c3aa5d6e2da00ec07295407594c566a55e0a5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.0625</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1785467398</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0x4449ee9e19610ed1a6459a4ec622295d3b7f27785ad56fb418383aa2562ee601</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.5987</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>FK Pardubice vs FK Jablonec</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>FK Pardubice</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>FK Jablonec</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0x6f33961a8aeffc315ff5d4a74c7a39f6142a8a7935508f048474d0ff32992a6d</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19527406</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1785415503</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1785693600</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>58.455115</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>0x19f2092f5b69321f498e3935667243b7f359a9876c356076e23b9a65276c6308</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>0.99998</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>1.8363</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>AC Sparta Praha</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>First League</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>AC Sparta Praha vs FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>AC Sparta Praha</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>0x030b420c1d99e5824e84934cc2cf515e30fa8607adbe9c86574bc07d04d89b58</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>L19527404</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>1785344291</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>1785517200</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>1.195791</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/First League/trades.xlsx
+++ b/data/sxbet/ligas/First League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,27 +531,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x750959461898d7985dfb52df9d12bdc41ab62fe003f6662c5f2c1f5e6883c3b3</t>
+          <t>0xcd7eeb23cf4653b67ca8bb338500599d76f786fabd895e39f8798d81a5e6323c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xee1ab015EDA6cAfd429804B0f31BABdaa77A9814</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>50.84999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -559,11 +555,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>FC Fastav Zlín</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>First League</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+          <t>FK Pardubice vs FK Jablonec</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>AC Sparta Praha</t>
+          <t>FK Pardubice</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>FC Fastav Zlín</t>
+          <t>FK Jablonec</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0x6f33961a8aeffc315ff5d4a74c7a39f6142a8a7935508f048474d0ff32992a6d</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19527404</t>
+          <t>L19527406</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785502250</t>
+          <t>1785528294</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785517200</t>
+          <t>1785693600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>86.36941</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,27 +635,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x8f3fc6c2b9b98811247c39740afa1dcc5d19110f7099bc28c5d7d72ac810cac5</t>
+          <t>0xd91ff81992be8b2712afdfb912135ecb5edf2939d6a4db7c57c68c2722d592e9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xee1ab015EDA6cAfd429804B0f31BABdaa77A9814</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11.61173</t>
+          <t>135.6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.0713</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -671,11 +659,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>FC Fastav Zlín</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>First League</t>
@@ -683,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+          <t>FK Pardubice vs FK Jablonec</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>AC Sparta Praha</t>
+          <t>FK Pardubice</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>FC Fastav Zlín</t>
+          <t>FK Jablonec</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0x6f33961a8aeffc315ff5d4a74c7a39f6142a8a7935508f048474d0ff32992a6d</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19527404</t>
+          <t>L19527406</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785499628</t>
+          <t>1785527602</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785517200</t>
+          <t>1785693600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>162.971649</t>
+          <t>230.318471</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,27 +739,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x5826b25b9a78e0be2b5364f99906ff8cc4bf845a562a5ea97f684cd2f19405ae</t>
+          <t>0xd0366ec96f7017f4a63bc4b2e4ebb5d39eeccee47bf6b8a301eb928a96289f52</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13.2855</t>
+          <t>236.1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -783,11 +763,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1.FC Slovacko</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>First League</t>
@@ -795,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.FC Slovacko vs Sk Artis Brno</t>
+          <t>FK Pardubice vs FK Jablonec</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.FC Slovacko</t>
+          <t>FK Pardubice</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Sk Artis Brno</t>
+          <t>FK Jablonec</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x10b10a8752de2c6583c0e8fbd3093ad3016bc296293b0a09ba25166e401e636f</t>
+          <t>0x6f33961a8aeffc315ff5d4a74c7a39f6142a8a7935508f048474d0ff32992a6d</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19527405</t>
+          <t>L19527406</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785483401</t>
+          <t>1785526660</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785596400</t>
+          <t>1785693600</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>22.1425</t>
+          <t>403.589744</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,28 +843,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xe630cfdee3f17d67e170b23665fcaae89fd50d2dc2f339c76f4a1abe7a079fc6</t>
+          <t>0xc3aab9ea873e401290c717d19347d28f917a39321f676c164221017f2c4f6d26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>14.025</t>
+          <t>129.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.425</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -899,27 +875,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+          <t>FK Pardubice vs FK Jablonec</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AC Sparta Praha</t>
+          <t>FK Pardubice</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>FC Fastav Zlín</t>
+          <t>FK Jablonec</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xaeedc6f6ec1744a71bd9be08dbc5f609f00c2c03449f55bd855097430952e5b5</t>
+          <t>0x6f33961a8aeffc315ff5d4a74c7a39f6142a8a7935508f048474d0ff32992a6d</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19527404</t>
+          <t>L19527406</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +920,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785476192</t>
+          <t>1785526441</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785517200</t>
+          <t>1785693600</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>222.051282</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,12 +947,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x5743b3baab7d0b4196ffe72f2ea5f72938b9bc8bd6e7156319c249a8e1d4977e</t>
+          <t>0x43f3a22ec8c07dd422bafc1fde911110bd1fcf76ec6e3223dd7f0aed6e1e8c32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -986,47 +962,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>561.59</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.8625</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>AC Sparta Praha -1.5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>First League</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>FC Fastav Zlín</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0xaeedc6f6ec1744a71bd9be08dbc5f609f00c2c03449f55bd855097430952e5b5</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1056,7 +1032,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785467456</t>
+          <t>1785522584</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1042,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>651.118841</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,12 +1059,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xdd3c48b46e7e419535742c6600d8d5c0bfbf337cf9d7384d0931d8644057b38b</t>
+          <t>0x54a5bfed73fa9849dcf3c9ec20db093d4727ca6b0097b619ed0edf38cae6f786</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1098,47 +1074,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (6)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>Over 6.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>First League</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>FC Fastav Zlín</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0xb34ca730dcc7f54317a0865c106f241bf3a0a92c92196610aae83f31b4fde7cf</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1168,7 +1144,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785467455</t>
+          <t>1785522482</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1178,7 +1154,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>717.55102</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,12 +1171,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x1c93771d6891dfab8458278bde673acf937ec233145cec08e5cbbf6abad22ca4</t>
+          <t>0x74bef36218276f8a8dc263acd5bdecf47dca9d1da52107936629591871506f66</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1210,12 +1186,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.1187</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1225,32 +1201,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>First League</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>FC Fastav Zlín</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1280,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785467402</t>
+          <t>1785522084</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1290,7 +1266,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>8.421053</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,12 +1283,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x94f51445b33e0f282b7b2e2a657f02ae3b738ee45fa16dda9267fc320dd63f2e</t>
+          <t>0xa60b660b68bf7aa460ac28ece86361bd9b81b3afbe90ef8eeccd9e606cc373d1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1322,47 +1298,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>465.34996</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.8137</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>AC Sparta Praha -1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>First League</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>FC Fastav Zlín</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0x17f4400365fa7a79fe731d223b8adaf52b973c2439ae958d1df9247114bdedf4</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1392,7 +1368,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785467401</t>
+          <t>1785521489</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1402,7 +1378,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>571.85863</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,12 +1395,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x7a2d2b6948d276131073d7eb95625bb09fee93e0072e6618ec7171f59bef3d9a</t>
+          <t>0xfe64a2f01ed09b6609747707cecfedc4abd0b70f5a9fd9bd6038e8d838ff56dd</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1434,12 +1410,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.1075</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1449,32 +1425,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>First League</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>FC Fastav Zlín</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1504,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785467400</t>
+          <t>1785521462</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1514,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>46.604651</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1531,12 +1507,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xb45d6395ce739a0bf97a9c585d0c3aa5d6e2da00ec07295407594c566a55e0a5</t>
+          <t>0x1f1895b7ed0e024447b5b3f943357fc14c356a4ea72a5326707cdedd1e24135c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1546,12 +1522,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>35.77</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.0263</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1616,7 +1592,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785467398</t>
+          <t>1785521188</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1626,7 +1602,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>1362.666667</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1643,23 +1619,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x4449ee9e19610ed1a6459a4ec622295d3b7f27785ad56fb418383aa2562ee601</t>
+          <t>0xeb885381a3c9b496731799dfbf94b00df9170923fb97343c35ef9b8f62f6a174</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.0275</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1667,7 +1647,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>First League</t>
@@ -1675,27 +1659,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FK Pardubice vs FK Jablonec</t>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>FK Pardubice</t>
+          <t>AC Sparta Praha</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>FK Jablonec</t>
+          <t>FC Fastav Zlín</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x6f33961a8aeffc315ff5d4a74c7a39f6142a8a7935508f048474d0ff32992a6d</t>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19527406</t>
+          <t>L19527404</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1720,17 +1704,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785415503</t>
+          <t>1785520736</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785693600</t>
+          <t>1785517200</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>58.455115</t>
+          <t>1530.181818</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1747,110 +1731,7486 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>0xc84bda0713cd7039e57a11fc2c18623d3d788ae35d317eacfc27592150d06087</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.1087</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1785520707</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>64.367816</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0xe19e040c07a307d4377c1bf76d1e33658e07dda00757036b59061f520332f8d7</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.0263</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1785520632</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1409.52381</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0x630cba50cd4b109e56cd381045573767a16cb8f5e32ab1a9fcebb7bd4b239b5d</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>700.31995</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.8975</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0x030b420c1d99e5824e84934cc2cf515e30fa8607adbe9c86574bc07d04d89b58</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1785518178</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>780.30078</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0xf298533d40386abae51813d63e78249bbe8e60f08339f98f451363323f5ee638</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>81.41</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.8975</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0x030b420c1d99e5824e84934cc2cf515e30fa8607adbe9c86574bc07d04d89b58</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1785518176</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>90.707521</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0xe582aa1900aecbc2735910569bc6efccb0291c488ee346b16e0600cf4ef2cdf7</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>285.47998</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.8738</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha -1</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0x17f4400365fa7a79fe731d223b8adaf52b973c2439ae958d1df9247114bdedf4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1785518175</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>326.729591</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0x8d114123249198d6573903919a89f63c323ba32dc14ae34819a8749520b86345</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>348.57999</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.8975</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0x030b420c1d99e5824e84934cc2cf515e30fa8607adbe9c86574bc07d04d89b58</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1785518175</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>388.389961</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0x47d809ee4299f6596b2a147d72d3c977ca8710308c2c1975ef427e4271d3c4c0</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>154.53999</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.7963</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0x030b420c1d99e5824e84934cc2cf515e30fa8607adbe9c86574bc07d04d89b58</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1785517808</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>194.08476</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0xea697fc7110abcb826b49f86cf405aceb01d50286e0c30e45d5cf7d322e34f5f</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>255.02999</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.7963</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0x030b420c1d99e5824e84934cc2cf515e30fa8607adbe9c86574bc07d04d89b58</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1785517765</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>320.288841</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0x5d4530c00e51d18a5d9d1112b9e1b3e6dbdf679c5d6aff904c86b51eec132652</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>70.83</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.1738</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0x0fde1fddd93b208b86d9402003ecf64fed31a1e1067800b54661bb327defe7cf</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1785517600</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>407.654676</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0x4c051f635fa5d992e5f338a9a303fe88beb88c3582652b7df3a4d2a545dbda38</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>247.92197</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.7963</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0x030b420c1d99e5824e84934cc2cf515e30fa8607adbe9c86574bc07d04d89b58</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1785517597</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>311.361972</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0xc72f5cd1828e0fe974599c8d207111b9b63d0b32697c9f6512a491b6943b2647</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>9.99984</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.9413</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1785516171</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>10.624</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0xc3e3205c88f7ce7b393990f14e58317f5f41ee2da197c6378bbb543474e46f65</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>8.84</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.2437</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0x17bd42fda28648e8338be0af912b657253911e68fcb62f740a132891d7db7ae6</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1785516114</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>36.266667</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0xae330bc7eee4cdca244b8c6f23027742138d5c74933a8c9f99b6b3dc6d7828d1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1785516084</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>7.142857</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0x9d304b611e2ff70e9c2bdb1e8169818a3fcc0db638b2c29ef1b8e4d149190ac1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>13.69</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1785516084</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>97.785714</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0x820e04065025c36b07aa20d679c5d3e7127b51ed0f6e41b9e266c33c762e776a</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.1425</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1785515691</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>26.385965</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0xcedd97467c70e982aba34c154f00e3af00e125c2346992d6fce55441c9c65c61</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.1412</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1785515690</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>13.946903</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0xa381410ffa84d755548f5e63cce38942a445d53214e17a74f3fe2e3b3353d47d</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>33.55988</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1785515648</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>35.702</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0x233432beef98ecf3af53a4241be8e3c237c00ba53f5a9ac64e7da80a2dd28e53</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.1412</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1785515584</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>13.876106</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0x17a378a79f97461cd23804f731d1433e08edde1d96a16650da6f3cbbb6cbd722</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>151.7299</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.9387</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1785515530</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>161.62972</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0xf7d4892d1ff0edb6c0bbf257734f24f123fb235aa1f9082e13c57e39ffbc4295</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.1412</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1785515516</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>25.274336</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0xf1d12812b1288093cdaa96116ad2ac735935e7a2b15b0ce86f7899c5d8c3ce26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>27.89996</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.9387</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1785515516</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>29.72033</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0x593b5359227a19bb892530dc7544b35e928a00461aae30262b8519819ea02795</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.1412</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1785515474</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>53.097345</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0x289538bf3b48ff9555ee4cf80bc4f23a5464a8c0c54ec603baaedf509bc79d45</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>140.68989</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.9387</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1785515474</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>149.86939</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0xf846d8aaecd70a692231ca406c6f62f7a4f3d6e35c1a3823e6885f819e92e416</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>168.59</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.9387</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1785515444</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>179.58988</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0x3ed03c2ad4bf86d806177e853d58caa9ab4db9ba17928f2cbbe0c6c3b5a97723</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1785515276</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>26.785714</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0x8a7d3aa110d16bbb7e56b0ea62a9250482ff542213d7b1caa3853654505be4b5</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>21.62987</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1785515207</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>23.0105</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0xeeb567364a6aee23023c0a93a1d529a52aa688b605bde21163c697f4ac3eb4c8</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>117.13998</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1785515000</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>124.617</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0x63aef270a8011afc5987b13beffa55d36ad30b7a3bb770f22aa9ba98dc9472e2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>7.49</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1785514999</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>53.5</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0xc2aad839f674a97b1ab10c521cb10381fc8ae16f7f16665d6480589562d3befb</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>15.56</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.1387</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1785514986</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>112.144144</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0x5439b273bf942aee08b9a219b7128d97d3d79c8646be7eb067c99d6505080436</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.1425</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1785514549</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>8.842105</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0x9b561650fa2b4d8b0fa546dcb5cd184da62badf119b17a1132c1bb308493a8ca</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1785514548</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>16.357143</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0x465eba41134d494de915d596d629ee8df83b7d9a7df941d2b216d1e16df1b1ae</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.1412</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1785514548</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>17.486726</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0x1f74aec85cf3debcff763283cc90112a168b672f3c0eb609c71073d7b2bbbe6b</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1785514484</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>7.142857</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0x82e9b2e415fb64e8789e843f9dd378a743266d70ee0f994275232fc114890530</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>168.59</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.9387</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1785514483</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>179.58988</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0x41036d1272acaec26b0c4ec038c7973a5e045919a09e6177ac9ebc3a65c59946</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1785514483</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>17.642857</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0x419057c394ad0c0faf05a829f6f15bf3c6c8e0d950193e608ea65b817ee70574</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>168.59</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.9387</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1785514420</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>179.58988</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0x34142f73e9f3d893d3ffc47e4577d9857d86dc61419c283d9db66ba35d54dc2a</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1785514360</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>17.642857</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0x9bfee118956bd4a80cd08d41debb3955419a9c28e34be992682d8498146d4b8e</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>5.76</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1785514359</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>41.142857</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0x7bfa96805a6d5829a95ac6abc0abf5e4a2edcb375c8578d7e5d74a6d32d25c09</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>97.55</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.9387</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1785514359</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>103.91478</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0x53056e82a7e9585ef2e84c4816048c79cf84861a2fc5082332c76859618023b3</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>23.22997</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.9387</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1785513856</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>24.74564</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0x13bb508594422d2b5d84af636d552d9173c10a5ff0d706a52651dc95b539e028</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>47.80989</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.9387</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1785513771</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>50.92931</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0xabb562a0f65c42adddcc189e3e2215337f676e4ec5625b45a0e0cb342699b80f</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.1412</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1785513521</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>9.486726</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0x9ba8f8612d4d8d87783ad078e3420357552308b8b17de6c858b3695acbbc3690</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.1412</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1785513520</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>8.424779</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0x733e8856cd5d8ea10cdc80458c099b8d7fb15ef93d66b5550c0bb79e939859c1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.1412</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1785513520</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>7.079646</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0x4bbb3b82255ad658fcbd378a2ac89a39395a1c78fba5ec8d41b9774e024f4802</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.1425</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1785513008</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>7.017544</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0x0fe5752caa9a1977e0737de1c91d6d53b5495b36423cf81d570278f2711b3f5b</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>0.24959</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.1425</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1785513008</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1.751509</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0xa3bdd8b8ff3bf39e5448003bc394cd3796665c55ff8c8c6bc5ac382c133b7024</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.1412</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1785513007</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>10.619469</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0xa5edb3f37ae608ef75267c2cfcc037e5fbfaa5c6366a608c9aa980b89edb0c18</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1.49768</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1785513004</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>10.697714</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0x4c92ea975f4abfd11528ad3bd5068772fef73fc5a9c496a82a3bdaac4f15e6ae</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1785512832</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0x2781ccfcd140d963dd66d6d323bf6ff38972a379ee031aeea31fb78b5791ce74</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1785512464</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>27.928571</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0x783263e4f019377a4c97fec50249683c0a1e62f9d9bd3ed5f8174d30a348557a</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1785512364</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>11.785714</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0x4e0b58eaeb16d9a65223a526ad9c776618226743096b9090a4d65a9784c1b333</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.1387</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1785512363</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>19.387387</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0x1cf330e4b50b7c08e976e241123a89fa08540c3fcf5cf020bfee05321656bc23</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.1387</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>1785512358</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>9.441441</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0x2ab8217ba40b7d55f9f94a8ff17315cddb81f645825672f8934577312b36daea</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2.0026</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.1387</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1785510257</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>14.433153</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0x7679ba883bb4f90f7e6ce75ff574661b0ebf6ca4da6040e4aea89ece118a5bdd</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2.70315</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.1387</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1785507591</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>19.482162</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0x1e93b209beeae1a06c7ea8de1ae2cad5377c028685459f1b2ce613ad5f4e1198</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.1387</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1785507591</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>30.990991</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0x750959461898d7985dfb52df9d12bdc41ab62fe003f6662c5f2c1f5e6883c3b3</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>15.12</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1785502250</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>216.0</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0x8f3fc6c2b9b98811247c39740afa1dcc5d19110f7099bc28c5d7d72ac810cac5</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>11.61173</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.0713</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>1785499628</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>162.971649</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0x5826b25b9a78e0be2b5364f99906ff8cc4bf845a562a5ea97f684cd2f19405ae</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>13.2855</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1.FC Slovacko</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1.FC Slovacko vs Sk Artis Brno</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>1.FC Slovacko</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Sk Artis Brno</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0x10b10a8752de2c6583c0e8fbd3093ad3016bc296293b0a09ba25166e401e636f</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>L19527405</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1785483401</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1785596400</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>22.1425</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0xe630cfdee3f17d67e170b23665fcaae89fd50d2dc2f339c76f4a1abe7a079fc6</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>14.025</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.425</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0xaeedc6f6ec1744a71bd9be08dbc5f609f00c2c03449f55bd855097430952e5b5</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1785476192</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0x5743b3baab7d0b4196ffe72f2ea5f72938b9bc8bd6e7156319c249a8e1d4977e</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.0625</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>1785467456</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0xdd3c48b46e7e419535742c6600d8d5c0bfbf337cf9d7384d0931d8644057b38b</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1.0625</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1785467455</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0x1c93771d6891dfab8458278bde673acf937ec233145cec08e5cbbf6abad22ca4</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.0625</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>1785467402</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0x94f51445b33e0f282b7b2e2a657f02ae3b738ee45fa16dda9267fc320dd63f2e</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1.0625</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>1785467401</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0x7a2d2b6948d276131073d7eb95625bb09fee93e0072e6618ec7171f59bef3d9a</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1.0625</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1785467400</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0xb45d6395ce739a0bf97a9c585d0c3aa5d6e2da00ec07295407594c566a55e0a5</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.0625</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>1785467398</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0x4449ee9e19610ed1a6459a4ec622295d3b7f27785ad56fb418383aa2562ee601</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1.5987</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>FK Pardubice vs FK Jablonec</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>FK Pardubice</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>FK Jablonec</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0x6f33961a8aeffc315ff5d4a74c7a39f6142a8a7935508f048474d0ff32992a6d</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>L19527406</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>1785415503</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>1785693600</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>58.455115</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>0x19f2092f5b69321f498e3935667243b7f359a9876c356076e23b9a65276c6308</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
         <is>
           <t>0.99998</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>1.8363</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>AC Sparta Praha</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>First League</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>AC Sparta Praha vs FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>AC Sparta Praha</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>0x030b420c1d99e5824e84934cc2cf515e30fa8607adbe9c86574bc07d04d89b58</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>L19527404</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
         <is>
           <t>1785344291</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>1785517200</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>1.195791</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U80" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V80" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/First League/trades.xlsx
+++ b/data/sxbet/ligas/First League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V80"/>
+  <dimension ref="A1:V82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xcd7eeb23cf4653b67ca8bb338500599d76f786fabd895e39f8798d81a5e6323c</t>
+          <t>0xaf3a4eefdd4ffc17d56eaae83b1466fa115c1b23be0a62a1cb1857035b15dbe6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xee1ab015EDA6cAfd429804B0f31BABdaa77A9814</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>50.84999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.3813</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FK Pardubice vs FK Jablonec</t>
+          <t>1.FC Slovacko vs Sk Artis Brno</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>FK Pardubice</t>
+          <t>1.FC Slovacko</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>FK Jablonec</t>
+          <t>Sk Artis Brno</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x6f33961a8aeffc315ff5d4a74c7a39f6142a8a7935508f048474d0ff32992a6d</t>
+          <t>0x10b10a8752de2c6583c0e8fbd3093ad3016bc296293b0a09ba25166e401e636f</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19527406</t>
+          <t>L19527405</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785528294</t>
+          <t>1785574104</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785693600</t>
+          <t>1785596400</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>86.36941</t>
+          <t>2.622951</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,31 +635,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xd91ff81992be8b2712afdfb912135ecb5edf2939d6a4db7c57c68c2722d592e9</t>
+          <t>0x704a8a9a472241433e3934dd10b8a3cd1a4b9fc5c4caccd0bcf92d261bba85fa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xee1ab015EDA6cAfd429804B0f31BABdaa77A9814</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>135.6</t>
+          <t>91.45288</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.5675</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>First League</t>
@@ -667,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>FK Pardubice vs FK Jablonec</t>
+          <t>1.FC Slovacko vs Sk Artis Brno</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>FK Pardubice</t>
+          <t>1.FC Slovacko</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>FK Jablonec</t>
+          <t>Sk Artis Brno</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x6f33961a8aeffc315ff5d4a74c7a39f6142a8a7935508f048474d0ff32992a6d</t>
+          <t>0xdf743daf96642865938eba198eea17330d0a6dee15b03b792fad0cbf1022f8c4</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19527406</t>
+          <t>L19527405</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785527602</t>
+          <t>1785560694</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785693600</t>
+          <t>1785596400</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>230.318471</t>
+          <t>161.150449</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,23 +747,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xd0366ec96f7017f4a63bc4b2e4ebb5d39eeccee47bf6b8a301eb928a96289f52</t>
+          <t>0xcd7eeb23cf4653b67ca8bb338500599d76f786fabd895e39f8798d81a5e6323c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
+          <t>0xee1ab015EDA6cAfd429804B0f31BABdaa77A9814</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>236.1</t>
+          <t>50.84999</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -816,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785526660</t>
+          <t>1785528294</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>403.589744</t>
+          <t>86.36941</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,23 +851,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xc3aab9ea873e401290c717d19347d28f917a39321f676c164221017f2c4f6d26</t>
+          <t>0xd91ff81992be8b2712afdfb912135ecb5edf2939d6a4db7c57c68c2722d592e9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
+          <t>0xee1ab015EDA6cAfd429804B0f31BABdaa77A9814</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>129.9</t>
+          <t>135.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -920,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785526441</t>
+          <t>1785527602</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -930,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>222.051282</t>
+          <t>230.318471</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,39 +955,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x43f3a22ec8c07dd422bafc1fde911110bd1fcf76ec6e3223dd7f0aed6e1e8c32</t>
+          <t>0xd0366ec96f7017f4a63bc4b2e4ebb5d39eeccee47bf6b8a301eb928a96289f52</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>561.59</t>
+          <t>236.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.8625</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>First League</t>
@@ -987,27 +987,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+          <t>FK Pardubice vs FK Jablonec</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>AC Sparta Praha</t>
+          <t>FK Pardubice</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>FC Fastav Zlín</t>
+          <t>FK Jablonec</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xaeedc6f6ec1744a71bd9be08dbc5f609f00c2c03449f55bd855097430952e5b5</t>
+          <t>0x6f33961a8aeffc315ff5d4a74c7a39f6142a8a7935508f048474d0ff32992a6d</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19527404</t>
+          <t>L19527406</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785522584</t>
+          <t>1785526660</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785517200</t>
+          <t>1785693600</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>651.118841</t>
+          <t>403.589744</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,39 +1059,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x54a5bfed73fa9849dcf3c9ec20db093d4727ca6b0097b619ed0edf38cae6f786</t>
+          <t>0xc3aab9ea873e401290c717d19347d28f917a39321f676c164221017f2c4f6d26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>129.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (6)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Over 6.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>First League</t>
@@ -1099,27 +1091,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+          <t>FK Pardubice vs FK Jablonec</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>AC Sparta Praha</t>
+          <t>FK Pardubice</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>FC Fastav Zlín</t>
+          <t>FK Jablonec</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xb34ca730dcc7f54317a0865c106f241bf3a0a92c92196610aae83f31b4fde7cf</t>
+          <t>0x6f33961a8aeffc315ff5d4a74c7a39f6142a8a7935508f048474d0ff32992a6d</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19527404</t>
+          <t>L19527406</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1144,17 +1136,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785522482</t>
+          <t>1785526441</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785517200</t>
+          <t>1785693600</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>717.55102</t>
+          <t>222.051282</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,12 +1163,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x74bef36218276f8a8dc263acd5bdecf47dca9d1da52107936629591871506f66</t>
+          <t>0x43f3a22ec8c07dd422bafc1fde911110bd1fcf76ec6e3223dd7f0aed6e1e8c32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1186,22 +1178,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>561.59</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.1187</t>
+          <t>1.8625</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>AC Sparta Praha -1.5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+          <t>0xaeedc6f6ec1744a71bd9be08dbc5f609f00c2c03449f55bd855097430952e5b5</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1256,7 +1248,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785522084</t>
+          <t>1785522584</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1266,7 +1258,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>8.421053</t>
+          <t>651.118841</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,7 +1275,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xa60b660b68bf7aa460ac28ece86361bd9b81b3afbe90ef8eeccd9e606cc373d1</t>
+          <t>0x54a5bfed73fa9849dcf3c9ec20db093d4727ca6b0097b619ed0edf38cae6f786</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1298,22 +1290,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>465.34996</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.8137</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (6)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AC Sparta Praha -1</t>
+          <t>Over 6.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1338,7 +1330,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x17f4400365fa7a79fe731d223b8adaf52b973c2439ae958d1df9247114bdedf4</t>
+          <t>0xb34ca730dcc7f54317a0865c106f241bf3a0a92c92196610aae83f31b4fde7cf</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1368,7 +1360,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785521489</t>
+          <t>1785522482</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1378,7 +1370,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>571.85863</t>
+          <t>717.55102</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,7 +1387,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xfe64a2f01ed09b6609747707cecfedc4abd0b70f5a9fd9bd6038e8d838ff56dd</t>
+          <t>0x74bef36218276f8a8dc263acd5bdecf47dca9d1da52107936629591871506f66</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1410,12 +1402,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.1075</t>
+          <t>1.1187</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1480,7 +1472,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785521462</t>
+          <t>1785522084</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1482,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>46.604651</t>
+          <t>8.421053</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,12 +1499,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x1f1895b7ed0e024447b5b3f943357fc14c356a4ea72a5326707cdedd1e24135c</t>
+          <t>0xa60b660b68bf7aa460ac28ece86361bd9b81b3afbe90ef8eeccd9e606cc373d1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1522,47 +1514,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>465.34996</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.0263</t>
+          <t>1.8137</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>AC Sparta Praha -1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>First League</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>FC Fastav Zlín</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0x17f4400365fa7a79fe731d223b8adaf52b973c2439ae958d1df9247114bdedf4</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1592,7 +1584,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785521188</t>
+          <t>1785521489</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1602,7 +1594,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1362.666667</t>
+          <t>571.85863</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,12 +1611,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xeb885381a3c9b496731799dfbf94b00df9170923fb97343c35ef9b8f62f6a174</t>
+          <t>0xfe64a2f01ed09b6609747707cecfedc4abd0b70f5a9fd9bd6038e8d838ff56dd</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1634,12 +1626,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.0275</t>
+          <t>1.1075</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1649,32 +1641,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>First League</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>FC Fastav Zlín</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1704,7 +1696,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785520736</t>
+          <t>1785521462</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1706,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1530.181818</t>
+          <t>46.604651</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,12 +1723,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xc84bda0713cd7039e57a11fc2c18623d3d788ae35d317eacfc27592150d06087</t>
+          <t>0x1f1895b7ed0e024447b5b3f943357fc14c356a4ea72a5326707cdedd1e24135c</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1746,12 +1738,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>35.77</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.1087</t>
+          <t>1.0263</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1761,7 +1753,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>FC Fastav Zlín</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1786,7 +1778,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1816,7 +1808,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785520707</t>
+          <t>1785521188</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1826,7 +1818,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>64.367816</t>
+          <t>1362.666667</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1843,7 +1835,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xe19e040c07a307d4377c1bf76d1e33658e07dda00757036b59061f520332f8d7</t>
+          <t>0xeb885381a3c9b496731799dfbf94b00df9170923fb97343c35ef9b8f62f6a174</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1858,12 +1850,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.0263</t>
+          <t>1.0275</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1928,7 +1920,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785520632</t>
+          <t>1785520736</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1938,7 +1930,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1409.52381</t>
+          <t>1530.181818</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1955,12 +1947,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x630cba50cd4b109e56cd381045573767a16cb8f5e32ab1a9fcebb7bd4b239b5d</t>
+          <t>0xc84bda0713cd7039e57a11fc2c18623d3d788ae35d317eacfc27592150d06087</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1970,12 +1962,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>700.31995</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.8975</t>
+          <t>1.1087</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1985,24 +1977,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>AC Sparta Praha</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>First League</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>FC Fastav Zlín</t>
@@ -2010,7 +2002,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x030b420c1d99e5824e84934cc2cf515e30fa8607adbe9c86574bc07d04d89b58</t>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2040,7 +2032,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785518178</t>
+          <t>1785520707</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2050,7 +2042,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>780.30078</t>
+          <t>64.367816</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2067,12 +2059,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xf298533d40386abae51813d63e78249bbe8e60f08339f98f451363323f5ee638</t>
+          <t>0xe19e040c07a307d4377c1bf76d1e33658e07dda00757036b59061f520332f8d7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2082,12 +2074,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>81.41</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.8975</t>
+          <t>1.0263</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2097,24 +2089,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>AC Sparta Praha</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>First League</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>FC Fastav Zlín</t>
@@ -2122,7 +2114,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x030b420c1d99e5824e84934cc2cf515e30fa8607adbe9c86574bc07d04d89b58</t>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2152,7 +2144,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785518176</t>
+          <t>1785520632</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2162,7 +2154,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>90.707521</t>
+          <t>1409.52381</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2179,7 +2171,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xe582aa1900aecbc2735910569bc6efccb0291c488ee346b16e0600cf4ef2cdf7</t>
+          <t>0x630cba50cd4b109e56cd381045573767a16cb8f5e32ab1a9fcebb7bd4b239b5d</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2194,22 +2186,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>285.47998</t>
+          <t>700.31995</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.8738</t>
+          <t>1.8975</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>AC Sparta Praha -1</t>
+          <t>AC Sparta Praha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2234,7 +2226,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x17f4400365fa7a79fe731d223b8adaf52b973c2439ae958d1df9247114bdedf4</t>
+          <t>0x030b420c1d99e5824e84934cc2cf515e30fa8607adbe9c86574bc07d04d89b58</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2264,7 +2256,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785518175</t>
+          <t>1785518178</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2274,7 +2266,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>326.729591</t>
+          <t>780.30078</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2291,7 +2283,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x8d114123249198d6573903919a89f63c323ba32dc14ae34819a8749520b86345</t>
+          <t>0xf298533d40386abae51813d63e78249bbe8e60f08339f98f451363323f5ee638</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2306,7 +2298,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>348.57999</t>
+          <t>81.41</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2376,7 +2368,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785518175</t>
+          <t>1785518176</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2386,7 +2378,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>388.389961</t>
+          <t>90.707521</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2403,7 +2395,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x47d809ee4299f6596b2a147d72d3c977ca8710308c2c1975ef427e4271d3c4c0</t>
+          <t>0xe582aa1900aecbc2735910569bc6efccb0291c488ee346b16e0600cf4ef2cdf7</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2418,39 +2410,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>154.53999</t>
+          <t>285.47998</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.8738</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>AC Sparta Praha -1</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>AC Sparta Praha</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>First League</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>FC Fastav Zlín</t>
@@ -2458,7 +2450,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x030b420c1d99e5824e84934cc2cf515e30fa8607adbe9c86574bc07d04d89b58</t>
+          <t>0x17f4400365fa7a79fe731d223b8adaf52b973c2439ae958d1df9247114bdedf4</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2488,7 +2480,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785517808</t>
+          <t>1785518175</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2498,7 +2490,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>194.08476</t>
+          <t>326.729591</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2515,7 +2507,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xea697fc7110abcb826b49f86cf405aceb01d50286e0c30e45d5cf7d322e34f5f</t>
+          <t>0x8d114123249198d6573903919a89f63c323ba32dc14ae34819a8749520b86345</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2530,12 +2522,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>255.02999</t>
+          <t>348.57999</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.8975</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2600,7 +2592,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785517765</t>
+          <t>1785518175</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2610,7 +2602,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>320.288841</t>
+          <t>388.389961</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2627,31 +2619,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x5d4530c00e51d18a5d9d1112b9e1b3e6dbdf679c5d6aff904c86b51eec132652</t>
+          <t>0x47d809ee4299f6596b2a147d72d3c977ca8710308c2c1975ef427e4271d3c4c0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>70.83</t>
+          <t>154.53999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.1738</t>
+          <t>1.7963</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>First League</t>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x0fde1fddd93b208b86d9402003ecf64fed31a1e1067800b54661bb327defe7cf</t>
+          <t>0x030b420c1d99e5824e84934cc2cf515e30fa8607adbe9c86574bc07d04d89b58</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785517600</t>
+          <t>1785517808</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>407.654676</t>
+          <t>194.08476</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2731,7 +2731,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x4c051f635fa5d992e5f338a9a303fe88beb88c3582652b7df3a4d2a545dbda38</t>
+          <t>0xea697fc7110abcb826b49f86cf405aceb01d50286e0c30e45d5cf7d322e34f5f</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>247.92197</t>
+          <t>255.02999</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785517597</t>
+          <t>1785517765</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>311.361972</t>
+          <t>320.288841</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2843,7 +2843,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xc72f5cd1828e0fe974599c8d207111b9b63d0b32697c9f6512a491b6943b2647</t>
+          <t>0x5d4530c00e51d18a5d9d1112b9e1b3e6dbdf679c5d6aff904c86b51eec132652</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2854,17 +2854,17 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>9.99984</t>
+          <t>70.83</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.9413</t>
+          <t>1.1738</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0x0fde1fddd93b208b86d9402003ecf64fed31a1e1067800b54661bb327defe7cf</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785516171</t>
+          <t>1785517600</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>10.624</t>
+          <t>407.654676</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2947,12 +2947,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xc3e3205c88f7ce7b393990f14e58317f5f41ee2da197c6378bbb543474e46f65</t>
+          <t>0x4c051f635fa5d992e5f338a9a303fe88beb88c3582652b7df3a4d2a545dbda38</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2962,22 +2962,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>247.92197</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.2437</t>
+          <t>1.7963</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>AC Sparta Praha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x17bd42fda28648e8338be0af912b657253911e68fcb62f740a132891d7db7ae6</t>
+          <t>0x030b420c1d99e5824e84934cc2cf515e30fa8607adbe9c86574bc07d04d89b58</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785516114</t>
+          <t>1785517597</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>36.266667</t>
+          <t>311.361972</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3059,7 +3059,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xae330bc7eee4cdca244b8c6f23027742138d5c74933a8c9f99b6b3dc6d7828d1</t>
+          <t>0xc72f5cd1828e0fe974599c8d207111b9b63d0b32697c9f6512a491b6943b2647</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3067,19 +3067,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9.99984</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.9413</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3087,11 +3083,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>First League</t>
@@ -3114,7 +3106,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3144,7 +3136,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785516084</t>
+          <t>1785516171</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3154,7 +3146,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>7.142857</t>
+          <t>10.624</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3171,7 +3163,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x9d304b611e2ff70e9c2bdb1e8169818a3fcc0db638b2c29ef1b8e4d149190ac1</t>
+          <t>0xc3e3205c88f7ce7b393990f14e58317f5f41ee2da197c6378bbb543474e46f65</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3186,22 +3178,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>13.69</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3226,7 +3218,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+          <t>0x17bd42fda28648e8338be0af912b657253911e68fcb62f740a132891d7db7ae6</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3256,7 +3248,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785516084</t>
+          <t>1785516114</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3266,7 +3258,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>97.785714</t>
+          <t>36.266667</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3283,7 +3275,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x820e04065025c36b07aa20d679c5d3e7127b51ed0f6e41b9e266c33c762e776a</t>
+          <t>0xae330bc7eee4cdca244b8c6f23027742138d5c74933a8c9f99b6b3dc6d7828d1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3298,12 +3290,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.1425</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3368,7 +3360,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785515691</t>
+          <t>1785516084</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3378,7 +3370,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>26.385965</t>
+          <t>7.142857</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3395,7 +3387,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xcedd97467c70e982aba34c154f00e3af00e125c2346992d6fce55441c9c65c61</t>
+          <t>0x9d304b611e2ff70e9c2bdb1e8169818a3fcc0db638b2c29ef1b8e4d149190ac1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3410,12 +3402,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.1412</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3480,7 +3472,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785515690</t>
+          <t>1785516084</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3490,7 +3482,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>13.946903</t>
+          <t>97.785714</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3507,7 +3499,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xa381410ffa84d755548f5e63cce38942a445d53214e17a74f3fe2e3b3353d47d</t>
+          <t>0x820e04065025c36b07aa20d679c5d3e7127b51ed0f6e41b9e266c33c762e776a</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3515,15 +3507,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>33.55988</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.1425</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3531,7 +3527,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>First League</t>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785515648</t>
+          <t>1785515691</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>35.702</t>
+          <t>26.385965</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3611,7 +3611,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x233432beef98ecf3af53a4241be8e3c237c00ba53f5a9ac64e7da80a2dd28e53</t>
+          <t>0xcedd97467c70e982aba34c154f00e3af00e125c2346992d6fce55441c9c65c61</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785515584</t>
+          <t>1785515690</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>13.876106</t>
+          <t>13.946903</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x17a378a79f97461cd23804f731d1433e08edde1d96a16650da6f3cbbb6cbd722</t>
+          <t>0xa381410ffa84d755548f5e63cce38942a445d53214e17a74f3fe2e3b3353d47d</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3734,12 +3734,12 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>151.7299</t>
+          <t>33.55988</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.9387</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785515530</t>
+          <t>1785515648</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>161.62972</t>
+          <t>35.702</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3827,7 +3827,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xf7d4892d1ff0edb6c0bbf257734f24f123fb235aa1f9082e13c57e39ffbc4295</t>
+          <t>0x233432beef98ecf3af53a4241be8e3c237c00ba53f5a9ac64e7da80a2dd28e53</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785515516</t>
+          <t>1785515584</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>25.274336</t>
+          <t>13.876106</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3939,7 +3939,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xf1d12812b1288093cdaa96116ad2ac735935e7a2b15b0ce86f7899c5d8c3ce26</t>
+          <t>0x17a378a79f97461cd23804f731d1433e08edde1d96a16650da6f3cbbb6cbd722</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3950,7 +3950,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>27.89996</t>
+          <t>151.7299</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785515516</t>
+          <t>1785515530</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>29.72033</t>
+          <t>161.62972</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4043,7 +4043,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x593b5359227a19bb892530dc7544b35e928a00461aae30262b8519819ea02795</t>
+          <t>0xf7d4892d1ff0edb6c0bbf257734f24f123fb235aa1f9082e13c57e39ffbc4295</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785515474</t>
+          <t>1785515516</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>53.097345</t>
+          <t>25.274336</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4155,7 +4155,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x289538bf3b48ff9555ee4cf80bc4f23a5464a8c0c54ec603baaedf509bc79d45</t>
+          <t>0xf1d12812b1288093cdaa96116ad2ac735935e7a2b15b0ce86f7899c5d8c3ce26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4166,7 +4166,7 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>140.68989</t>
+          <t>27.89996</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785515474</t>
+          <t>1785515516</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>149.86939</t>
+          <t>29.72033</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4259,7 +4259,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xf846d8aaecd70a692231ca406c6f62f7a4f3d6e35c1a3823e6885f819e92e416</t>
+          <t>0x593b5359227a19bb892530dc7544b35e928a00461aae30262b8519819ea02795</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4267,15 +4267,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>168.59</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.9387</t>
+          <t>1.1412</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4283,7 +4287,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>First League</t>
@@ -4306,7 +4314,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4336,7 +4344,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785515444</t>
+          <t>1785515474</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4346,7 +4354,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>179.58988</t>
+          <t>53.097345</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4363,7 +4371,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x3ed03c2ad4bf86d806177e853d58caa9ab4db9ba17928f2cbbe0c6c3b5a97723</t>
+          <t>0x289538bf3b48ff9555ee4cf80bc4f23a5464a8c0c54ec603baaedf509bc79d45</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4371,19 +4379,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>140.68989</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.9387</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4391,11 +4395,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>First League</t>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785515276</t>
+          <t>1785515474</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>26.785714</t>
+          <t>149.86939</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4475,7 +4475,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x8a7d3aa110d16bbb7e56b0ea62a9250482ff542213d7b1caa3853654505be4b5</t>
+          <t>0xf846d8aaecd70a692231ca406c6f62f7a4f3d6e35c1a3823e6885f819e92e416</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4486,12 +4486,12 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>21.62987</t>
+          <t>168.59</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.9387</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785515207</t>
+          <t>1785515444</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>23.0105</t>
+          <t>179.58988</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4579,7 +4579,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xeeb567364a6aee23023c0a93a1d529a52aa688b605bde21163c697f4ac3eb4c8</t>
+          <t>0x3ed03c2ad4bf86d806177e853d58caa9ab4db9ba17928f2cbbe0c6c3b5a97723</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4587,15 +4587,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>117.13998</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4603,7 +4607,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>First League</t>
@@ -4626,7 +4634,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4656,7 +4664,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785515000</t>
+          <t>1785515276</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4666,7 +4674,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>124.617</t>
+          <t>26.785714</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4683,7 +4691,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x63aef270a8011afc5987b13beffa55d36ad30b7a3bb770f22aa9ba98dc9472e2</t>
+          <t>0x8a7d3aa110d16bbb7e56b0ea62a9250482ff542213d7b1caa3853654505be4b5</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4691,19 +4699,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>21.62987</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4711,11 +4715,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>First League</t>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785514999</t>
+          <t>1785515207</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>23.0105</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4795,7 +4795,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xc2aad839f674a97b1ab10c521cb10381fc8ae16f7f16665d6480589562d3befb</t>
+          <t>0xeeb567364a6aee23023c0a93a1d529a52aa688b605bde21163c697f4ac3eb4c8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4803,19 +4803,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>117.13998</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.1387</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4823,11 +4819,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>First League</t>
@@ -4850,7 +4842,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4880,7 +4872,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785514986</t>
+          <t>1785515000</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4890,7 +4882,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>112.144144</t>
+          <t>124.617</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4907,7 +4899,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x5439b273bf942aee08b9a219b7128d97d3d79c8646be7eb067c99d6505080436</t>
+          <t>0x63aef270a8011afc5987b13beffa55d36ad30b7a3bb770f22aa9ba98dc9472e2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4922,12 +4914,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.1425</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4992,7 +4984,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785514549</t>
+          <t>1785514999</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5002,7 +4994,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>8.842105</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5019,7 +5011,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x9b561650fa2b4d8b0fa546dcb5cd184da62badf119b17a1132c1bb308493a8ca</t>
+          <t>0xc2aad839f674a97b1ab10c521cb10381fc8ae16f7f16665d6480589562d3befb</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5034,12 +5026,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.1387</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5104,7 +5096,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785514548</t>
+          <t>1785514986</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5114,7 +5106,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>16.357143</t>
+          <t>112.144144</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5131,7 +5123,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x465eba41134d494de915d596d629ee8df83b7d9a7df941d2b216d1e16df1b1ae</t>
+          <t>0x5439b273bf942aee08b9a219b7128d97d3d79c8646be7eb067c99d6505080436</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5146,12 +5138,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.1412</t>
+          <t>1.1425</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5216,7 +5208,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785514548</t>
+          <t>1785514549</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5226,7 +5218,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>17.486726</t>
+          <t>8.842105</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5243,7 +5235,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x1f74aec85cf3debcff763283cc90112a168b672f3c0eb609c71073d7b2bbbe6b</t>
+          <t>0x9b561650fa2b4d8b0fa546dcb5cd184da62badf119b17a1132c1bb308493a8ca</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5258,7 +5250,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5328,7 +5320,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785514484</t>
+          <t>1785514548</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5338,7 +5330,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>7.142857</t>
+          <t>16.357143</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5355,7 +5347,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x82e9b2e415fb64e8789e843f9dd378a743266d70ee0f994275232fc114890530</t>
+          <t>0x465eba41134d494de915d596d629ee8df83b7d9a7df941d2b216d1e16df1b1ae</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5363,15 +5355,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>168.59</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.9387</t>
+          <t>1.1412</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5379,7 +5375,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>First League</t>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785514483</t>
+          <t>1785514548</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>179.58988</t>
+          <t>17.486726</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5459,7 +5459,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x41036d1272acaec26b0c4ec038c7973a5e045919a09e6177ac9ebc3a65c59946</t>
+          <t>0x1f74aec85cf3debcff763283cc90112a168b672f3c0eb609c71073d7b2bbbe6b</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785514483</t>
+          <t>1785514484</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>17.642857</t>
+          <t>7.142857</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5571,7 +5571,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x419057c394ad0c0faf05a829f6f15bf3c6c8e0d950193e608ea65b817ee70574</t>
+          <t>0x82e9b2e415fb64e8789e843f9dd378a743266d70ee0f994275232fc114890530</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785514420</t>
+          <t>1785514483</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5675,7 +5675,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x34142f73e9f3d893d3ffc47e4577d9857d86dc61419c283d9db66ba35d54dc2a</t>
+          <t>0x41036d1272acaec26b0c4ec038c7973a5e045919a09e6177ac9ebc3a65c59946</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785514360</t>
+          <t>1785514483</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x9bfee118956bd4a80cd08d41debb3955419a9c28e34be992682d8498146d4b8e</t>
+          <t>0x419057c394ad0c0faf05a829f6f15bf3c6c8e0d950193e608ea65b817ee70574</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5795,19 +5795,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>168.59</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.9387</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5815,11 +5811,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>First League</t>
@@ -5842,7 +5834,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5872,7 +5864,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785514359</t>
+          <t>1785514420</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5882,7 +5874,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>41.142857</t>
+          <t>179.58988</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5899,7 +5891,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x7bfa96805a6d5829a95ac6abc0abf5e4a2edcb375c8578d7e5d74a6d32d25c09</t>
+          <t>0x34142f73e9f3d893d3ffc47e4577d9857d86dc61419c283d9db66ba35d54dc2a</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5907,15 +5899,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>97.55</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.9387</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5923,7 +5919,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>First League</t>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785514359</t>
+          <t>1785514360</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>103.91478</t>
+          <t>17.642857</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6003,7 +6003,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x53056e82a7e9585ef2e84c4816048c79cf84861a2fc5082332c76859618023b3</t>
+          <t>0x9bfee118956bd4a80cd08d41debb3955419a9c28e34be992682d8498146d4b8e</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6011,15 +6011,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>23.22997</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.9387</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6027,7 +6031,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>First League</t>
@@ -6050,7 +6058,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6080,7 +6088,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785513856</t>
+          <t>1785514359</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6090,7 +6098,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>24.74564</t>
+          <t>41.142857</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6107,7 +6115,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x13bb508594422d2b5d84af636d552d9173c10a5ff0d706a52651dc95b539e028</t>
+          <t>0x7bfa96805a6d5829a95ac6abc0abf5e4a2edcb375c8578d7e5d74a6d32d25c09</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6118,7 +6126,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>47.80989</t>
+          <t>97.55</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6184,7 +6192,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785513771</t>
+          <t>1785514359</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6194,7 +6202,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>50.92931</t>
+          <t>103.91478</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6211,7 +6219,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xabb562a0f65c42adddcc189e3e2215337f676e4ec5625b45a0e0cb342699b80f</t>
+          <t>0x53056e82a7e9585ef2e84c4816048c79cf84861a2fc5082332c76859618023b3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6219,19 +6227,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>23.22997</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.1412</t>
+          <t>1.9387</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6239,11 +6243,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>First League</t>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785513521</t>
+          <t>1785513856</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>9.486726</t>
+          <t>24.74564</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6323,7 +6323,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x9ba8f8612d4d8d87783ad078e3420357552308b8b17de6c858b3695acbbc3690</t>
+          <t>0x13bb508594422d2b5d84af636d552d9173c10a5ff0d706a52651dc95b539e028</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6331,19 +6331,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>47.80989</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.1412</t>
+          <t>1.9387</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6351,11 +6347,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>First League</t>
@@ -6378,7 +6370,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6408,7 +6400,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785513520</t>
+          <t>1785513771</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6418,7 +6410,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>8.424779</t>
+          <t>50.92931</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6435,7 +6427,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x733e8856cd5d8ea10cdc80458c099b8d7fb15ef93d66b5550c0bb79e939859c1</t>
+          <t>0xabb562a0f65c42adddcc189e3e2215337f676e4ec5625b45a0e0cb342699b80f</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6450,7 +6442,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6520,7 +6512,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785513520</t>
+          <t>1785513521</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6530,7 +6522,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>7.079646</t>
+          <t>9.486726</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6547,7 +6539,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x4bbb3b82255ad658fcbd378a2ac89a39395a1c78fba5ec8d41b9774e024f4802</t>
+          <t>0x9ba8f8612d4d8d87783ad078e3420357552308b8b17de6c858b3695acbbc3690</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6562,12 +6554,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.1425</t>
+          <t>1.1412</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6632,7 +6624,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785513008</t>
+          <t>1785513520</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6642,7 +6634,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>7.017544</t>
+          <t>8.424779</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6659,7 +6651,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x0fe5752caa9a1977e0737de1c91d6d53b5495b36423cf81d570278f2711b3f5b</t>
+          <t>0x733e8856cd5d8ea10cdc80458c099b8d7fb15ef93d66b5550c0bb79e939859c1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6674,12 +6666,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.24959</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.1425</t>
+          <t>1.1412</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6744,7 +6736,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785513008</t>
+          <t>1785513520</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6754,7 +6746,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1.751509</t>
+          <t>7.079646</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6771,7 +6763,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xa3bdd8b8ff3bf39e5448003bc394cd3796665c55ff8c8c6bc5ac382c133b7024</t>
+          <t>0x4bbb3b82255ad658fcbd378a2ac89a39395a1c78fba5ec8d41b9774e024f4802</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6786,12 +6778,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.1412</t>
+          <t>1.1425</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6856,7 +6848,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785513007</t>
+          <t>1785513008</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6866,7 +6858,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>10.619469</t>
+          <t>7.017544</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6883,7 +6875,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xa5edb3f37ae608ef75267c2cfcc037e5fbfaa5c6366a608c9aa980b89edb0c18</t>
+          <t>0x0fe5752caa9a1977e0737de1c91d6d53b5495b36423cf81d570278f2711b3f5b</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6898,12 +6890,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1.49768</t>
+          <t>0.24959</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.1425</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6968,7 +6960,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785513004</t>
+          <t>1785513008</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6978,7 +6970,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>10.697714</t>
+          <t>1.751509</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6995,7 +6987,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x4c92ea975f4abfd11528ad3bd5068772fef73fc5a9c496a82a3bdaac4f15e6ae</t>
+          <t>0xa3bdd8b8ff3bf39e5448003bc394cd3796665c55ff8c8c6bc5ac382c133b7024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7010,12 +7002,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.1412</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7080,7 +7072,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785512832</t>
+          <t>1785513007</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7090,7 +7082,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>10.619469</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7107,7 +7099,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x2781ccfcd140d963dd66d6d323bf6ff38972a379ee031aeea31fb78b5791ce74</t>
+          <t>0xa5edb3f37ae608ef75267c2cfcc037e5fbfaa5c6366a608c9aa980b89edb0c18</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7122,7 +7114,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>1.49768</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7192,7 +7184,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785512464</t>
+          <t>1785513004</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7202,7 +7194,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>27.928571</t>
+          <t>10.697714</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7219,7 +7211,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x783263e4f019377a4c97fec50249683c0a1e62f9d9bd3ed5f8174d30a348557a</t>
+          <t>0x4c92ea975f4abfd11528ad3bd5068772fef73fc5a9c496a82a3bdaac4f15e6ae</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7234,7 +7226,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7304,7 +7296,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785512364</t>
+          <t>1785512832</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7314,7 +7306,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>11.785714</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7331,7 +7323,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x4e0b58eaeb16d9a65223a526ad9c776618226743096b9090a4d65a9784c1b333</t>
+          <t>0x2781ccfcd140d963dd66d6d323bf6ff38972a379ee031aeea31fb78b5791ce74</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7346,12 +7338,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.1387</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7416,7 +7408,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785512363</t>
+          <t>1785512464</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7426,7 +7418,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>19.387387</t>
+          <t>27.928571</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7443,7 +7435,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x1cf330e4b50b7c08e976e241123a89fa08540c3fcf5cf020bfee05321656bc23</t>
+          <t>0x783263e4f019377a4c97fec50249683c0a1e62f9d9bd3ed5f8174d30a348557a</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7458,12 +7450,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.1387</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7528,7 +7520,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785512358</t>
+          <t>1785512364</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7538,7 +7530,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>9.441441</t>
+          <t>11.785714</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7555,12 +7547,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x2ab8217ba40b7d55f9f94a8ff17315cddb81f645825672f8934577312b36daea</t>
+          <t>0x4e0b58eaeb16d9a65223a526ad9c776618226743096b9090a4d65a9784c1b333</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7570,7 +7562,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2.0026</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7640,7 +7632,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785510257</t>
+          <t>1785512363</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7650,7 +7642,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>14.433153</t>
+          <t>19.387387</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7667,7 +7659,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x7679ba883bb4f90f7e6ce75ff574661b0ebf6ca4da6040e4aea89ece118a5bdd</t>
+          <t>0x1cf330e4b50b7c08e976e241123a89fa08540c3fcf5cf020bfee05321656bc23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7682,7 +7674,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2.70315</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7752,7 +7744,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785507591</t>
+          <t>1785512358</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7762,7 +7754,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>19.482162</t>
+          <t>9.441441</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7779,12 +7771,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x1e93b209beeae1a06c7ea8de1ae2cad5377c028685459f1b2ce613ad5f4e1198</t>
+          <t>0x2ab8217ba40b7d55f9f94a8ff17315cddb81f645825672f8934577312b36daea</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7794,7 +7786,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>2.0026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7864,7 +7856,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785507591</t>
+          <t>1785510257</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7874,7 +7866,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>30.990991</t>
+          <t>14.433153</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7891,12 +7883,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x750959461898d7985dfb52df9d12bdc41ab62fe003f6662c5f2c1f5e6883c3b3</t>
+          <t>0x7679ba883bb4f90f7e6ce75ff574661b0ebf6ca4da6040e4aea89ece118a5bdd</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7906,12 +7898,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>2.70315</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.1387</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7921,32 +7913,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t>FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>First League</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>FC Fastav Zlín</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7976,7 +7968,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785502250</t>
+          <t>1785507591</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7986,7 +7978,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>19.482162</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -8003,12 +7995,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x8f3fc6c2b9b98811247c39740afa1dcc5d19110f7099bc28c5d7d72ac810cac5</t>
+          <t>0x1e93b209beeae1a06c7ea8de1ae2cad5377c028685459f1b2ce613ad5f4e1198</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -8018,12 +8010,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>11.61173</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.0713</t>
+          <t>1.1387</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -8033,32 +8025,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t>FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>First League</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>FC Fastav Zlín</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0xe9609c1438c6a875f50d80b3e7094af45da58262e7a8c265df9f9ac9ce1eab83</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -8088,7 +8080,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785499628</t>
+          <t>1785507591</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -8098,7 +8090,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>162.971649</t>
+          <t>30.990991</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8115,12 +8107,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x5826b25b9a78e0be2b5364f99906ff8cc4bf845a562a5ea97f684cd2f19405ae</t>
+          <t>0x750959461898d7985dfb52df9d12bdc41ab62fe003f6662c5f2c1f5e6883c3b3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8130,12 +8122,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>13.2855</t>
+          <t>15.12</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8145,7 +8137,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1.FC Slovacko</t>
+          <t>FC Fastav Zlín</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8155,27 +8147,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1.FC Slovacko vs Sk Artis Brno</t>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>1.FC Slovacko</t>
+          <t>AC Sparta Praha</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Sk Artis Brno</t>
+          <t>FC Fastav Zlín</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0x10b10a8752de2c6583c0e8fbd3093ad3016bc296293b0a09ba25166e401e636f</t>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>L19527405</t>
+          <t>L19527404</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -8200,17 +8192,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785483401</t>
+          <t>1785502250</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>1785596400</t>
+          <t>1785517200</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>22.1425</t>
+          <t>216.0</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8227,31 +8219,39 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0xe630cfdee3f17d67e170b23665fcaae89fd50d2dc2f339c76f4a1abe7a079fc6</t>
+          <t>0x8f3fc6c2b9b98811247c39740afa1dcc5d19110f7099bc28c5d7d72ac810cac5</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>14.025</t>
+          <t>11.61173</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.425</t>
+          <t>1.0713</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>First League</t>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xaeedc6f6ec1744a71bd9be08dbc5f609f00c2c03449f55bd855097430952e5b5</t>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785476192</t>
+          <t>1785499628</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>162.971649</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8331,12 +8331,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x5743b3baab7d0b4196ffe72f2ea5f72938b9bc8bd6e7156319c249a8e1d4977e</t>
+          <t>0x5826b25b9a78e0be2b5364f99906ff8cc4bf845a562a5ea97f684cd2f19405ae</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8346,12 +8346,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13.2855</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>FC Fastav Zlín</t>
+          <t>1.FC Slovacko</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8371,27 +8371,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+          <t>1.FC Slovacko vs Sk Artis Brno</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>AC Sparta Praha</t>
+          <t>1.FC Slovacko</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>FC Fastav Zlín</t>
+          <t>Sk Artis Brno</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0x10b10a8752de2c6583c0e8fbd3093ad3016bc296293b0a09ba25166e401e636f</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>L19527404</t>
+          <t>L19527405</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8416,17 +8416,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785467456</t>
+          <t>1785483401</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>1785517200</t>
+          <t>1785596400</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>22.1425</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8443,62 +8443,54 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xdd3c48b46e7e419535742c6600d8d5c0bfbf337cf9d7384d0931d8644057b38b</t>
+          <t>0xe630cfdee3f17d67e170b23665fcaae89fd50d2dc2f339c76f4a1abe7a079fc6</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14.025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.425</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
         <is>
           <t>FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>First League</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha vs FC Fastav Zlín</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>AC Sparta Praha</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>FC Fastav Zlín</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+          <t>0xaeedc6f6ec1744a71bd9be08dbc5f609f00c2c03449f55bd855097430952e5b5</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8528,7 +8520,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785467455</t>
+          <t>1785476192</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8538,7 +8530,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8555,7 +8547,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x1c93771d6891dfab8458278bde673acf937ec233145cec08e5cbbf6abad22ca4</t>
+          <t>0x5743b3baab7d0b4196ffe72f2ea5f72938b9bc8bd6e7156319c249a8e1d4977e</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8570,7 +8562,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -8640,7 +8632,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785467402</t>
+          <t>1785467456</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8650,7 +8642,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8667,7 +8659,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x94f51445b33e0f282b7b2e2a657f02ae3b738ee45fa16dda9267fc320dd63f2e</t>
+          <t>0xdd3c48b46e7e419535742c6600d8d5c0bfbf337cf9d7384d0931d8644057b38b</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8682,7 +8674,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8752,7 +8744,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785467401</t>
+          <t>1785467455</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8762,7 +8754,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8779,7 +8771,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x7a2d2b6948d276131073d7eb95625bb09fee93e0072e6618ec7171f59bef3d9a</t>
+          <t>0x1c93771d6891dfab8458278bde673acf937ec233145cec08e5cbbf6abad22ca4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8864,7 +8856,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785467400</t>
+          <t>1785467402</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8891,7 +8883,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0xb45d6395ce739a0bf97a9c585d0c3aa5d6e2da00ec07295407594c566a55e0a5</t>
+          <t>0x94f51445b33e0f282b7b2e2a657f02ae3b738ee45fa16dda9267fc320dd63f2e</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8906,7 +8898,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -8976,7 +8968,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785467398</t>
+          <t>1785467401</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8986,7 +8978,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -9003,23 +8995,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x4449ee9e19610ed1a6459a4ec622295d3b7f27785ad56fb418383aa2562ee601</t>
+          <t>0x7a2d2b6948d276131073d7eb95625bb09fee93e0072e6618ec7171f59bef3d9a</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.0625</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -9027,7 +9023,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>First League</t>
@@ -9035,27 +9035,27 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>FK Pardubice vs FK Jablonec</t>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>FK Pardubice</t>
+          <t>AC Sparta Praha</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>FK Jablonec</t>
+          <t>FC Fastav Zlín</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x6f33961a8aeffc315ff5d4a74c7a39f6142a8a7935508f048474d0ff32992a6d</t>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>L19527406</t>
+          <t>L19527404</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -9080,17 +9080,17 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785415503</t>
+          <t>1785467400</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>1785693600</t>
+          <t>1785517200</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>58.455115</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -9107,110 +9107,326 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>0xb45d6395ce739a0bf97a9c585d0c3aa5d6e2da00ec07295407594c566a55e0a5</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.0625</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha vs FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>AC Sparta Praha</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>FC Fastav Zlín</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0x9500bf5b6846fee92a67b0c91fbfea74b8f7a29f9e2edf9a22ae104e172317f4</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>L19527404</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>1785467398</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0x4449ee9e19610ed1a6459a4ec622295d3b7f27785ad56fb418383aa2562ee601</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1.5987</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>First League</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>FK Pardubice vs FK Jablonec</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>FK Pardubice</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>FK Jablonec</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0x6f33961a8aeffc315ff5d4a74c7a39f6142a8a7935508f048474d0ff32992a6d</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>L19527406</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>1785415503</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>1785693600</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>58.455115</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>0x19f2092f5b69321f498e3935667243b7f359a9876c356076e23b9a65276c6308</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
         <is>
           <t>0.99998</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>1.8363</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>AC Sparta Praha</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>First League</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>AC Sparta Praha vs FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>AC Sparta Praha</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>FC Fastav Zlín</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>0x030b420c1d99e5824e84934cc2cf515e30fa8607adbe9c86574bc07d04d89b58</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>L19527404</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr">
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
         <is>
           <t>1785344291</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>1785517200</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>1.195791</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="U82" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr">
+      <c r="V82" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
